--- a/population_trend_tidy.xlsx
+++ b/population_trend_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/med mini project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{FCE9BF43-62DD-4509-B6FF-9613F1B348D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3B0CA24-B9CF-45E6-90A7-0421B5BAD9FD}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{FCE9BF43-62DD-4509-B6FF-9613F1B348D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D61F55DB-8198-46EE-B939-FE7C19B77081}"/>
   <bookViews>
-    <workbookView xWindow="4908" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5501DCC4-4A47-42B3-ABCF-C5797380A6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5501DCC4-4A47-42B3-ABCF-C5797380A6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Female</t>
+  </si>
+  <si>
+    <t>Australian Capital Territory</t>
   </si>
 </sst>
 </file>
@@ -125,7 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -133,7 +136,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -449,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71548FB8-35F0-4896-AC41-D8B6ED713676}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
@@ -459,10 +461,10 @@
     <col min="6" max="6" width="14" style="5" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" style="5" customWidth="1"/>
     <col min="8" max="8" width="11.77734375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.5546875" style="5" customWidth="1"/>
+    <col min="9" max="10" width="17.5546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,2887 +492,3860 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1971</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6567936</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2373784</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1799486</v>
+      </c>
+      <c r="E2" s="1">
+        <v>932976</v>
+      </c>
+      <c r="F2" s="1">
+        <v>597572</v>
+      </c>
+      <c r="G2" s="1">
+        <v>539332</v>
+      </c>
+      <c r="H2" s="1">
+        <v>199915</v>
+      </c>
+      <c r="I2" s="1">
+        <v>47750</v>
+      </c>
+      <c r="J2" s="1">
+        <v>77121</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1972</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6685153</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2407712</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1828978</v>
+      </c>
+      <c r="E3" s="1">
+        <v>956959</v>
+      </c>
+      <c r="F3" s="1">
+        <v>605054</v>
+      </c>
+      <c r="G3" s="1">
+        <v>553145</v>
+      </c>
+      <c r="H3" s="1">
+        <v>200926</v>
+      </c>
+      <c r="I3" s="1">
+        <v>50870</v>
+      </c>
+      <c r="J3" s="1">
+        <v>81509</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1973</v>
+      </c>
+      <c r="B4" s="1">
+        <v>6782848</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2428527</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1852056</v>
+      </c>
+      <c r="E4" s="1">
+        <v>984081</v>
+      </c>
+      <c r="F4" s="1">
+        <v>612069</v>
+      </c>
+      <c r="G4" s="1">
+        <v>562258</v>
+      </c>
+      <c r="H4" s="1">
+        <v>202119</v>
+      </c>
+      <c r="I4" s="1">
+        <v>53250</v>
+      </c>
+      <c r="J4" s="1">
+        <v>88488</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1974</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6889668</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2452418</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1875820</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1012648</v>
+      </c>
+      <c r="F5" s="1">
+        <v>618862</v>
+      </c>
+      <c r="G5" s="1">
+        <v>575430</v>
+      </c>
+      <c r="H5" s="1">
+        <v>203417</v>
+      </c>
+      <c r="I5" s="1">
+        <v>56045</v>
+      </c>
+      <c r="J5" s="1">
+        <v>95028</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1975</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6969181</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2467784</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1890499</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1033697</v>
+      </c>
+      <c r="F6" s="1">
+        <v>630495</v>
+      </c>
+      <c r="G6" s="1">
+        <v>588629</v>
+      </c>
+      <c r="H6" s="1">
+        <v>205265</v>
+      </c>
+      <c r="I6" s="1">
+        <v>51481</v>
+      </c>
+      <c r="J6" s="1">
+        <v>101331</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1976</v>
+      </c>
+      <c r="B7" s="1">
+        <v>7032034</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2476978</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1900488</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1053535</v>
+      </c>
+      <c r="F7" s="1">
+        <v>635152</v>
+      </c>
+      <c r="G7" s="1">
+        <v>599959</v>
+      </c>
+      <c r="H7" s="1">
+        <v>206193</v>
+      </c>
+      <c r="I7" s="1">
+        <v>54096</v>
+      </c>
+      <c r="J7" s="1">
+        <v>105633</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1977</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7104702</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2496098</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1911900</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1071295</v>
+      </c>
+      <c r="F8" s="1">
+        <v>640546</v>
+      </c>
+      <c r="G8" s="1">
+        <v>612145</v>
+      </c>
+      <c r="H8" s="1">
+        <v>207545</v>
+      </c>
+      <c r="I8" s="1">
+        <v>56828</v>
+      </c>
+      <c r="J8" s="1">
+        <v>108345</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1978</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7181293</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2519784</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1922930</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1091582</v>
+      </c>
+      <c r="F9" s="1">
+        <v>644711</v>
+      </c>
+      <c r="G9" s="1">
+        <v>623262</v>
+      </c>
+      <c r="H9" s="1">
+        <v>208859</v>
+      </c>
+      <c r="I9" s="1">
+        <v>60005</v>
+      </c>
+      <c r="J9" s="1">
+        <v>110160</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1979</v>
+      </c>
+      <c r="B10" s="1">
+        <v>7253762</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2546874</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1932332</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1112774</v>
+      </c>
+      <c r="F10" s="1">
+        <v>646249</v>
+      </c>
+      <c r="G10" s="1">
+        <v>632032</v>
+      </c>
+      <c r="H10" s="1">
+        <v>210314</v>
+      </c>
+      <c r="I10" s="1">
+        <v>61991</v>
+      </c>
+      <c r="J10" s="1">
+        <v>111196</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1980</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7338060</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2576617</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1944400</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1138297</v>
+      </c>
+      <c r="F11" s="1">
+        <v>650221</v>
+      </c>
+      <c r="G11" s="1">
+        <v>641935</v>
+      </c>
+      <c r="H11" s="1">
+        <v>211000</v>
+      </c>
+      <c r="I11" s="1">
+        <v>63219</v>
+      </c>
+      <c r="J11" s="1">
+        <v>112371</v>
+      </c>
+      <c r="K11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>1981</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B12" s="4">
         <v>7514339</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C12" s="4">
         <v>2624579</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D12" s="4">
         <v>1969349</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E12" s="4">
         <v>1200504</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F12" s="4">
         <v>657014</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G12" s="4">
         <v>667381</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H12" s="4">
         <v>212935</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I12" s="4">
         <v>68023</v>
       </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="J12" s="1">
+        <v>113605</v>
+      </c>
+      <c r="K12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>1982</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B13" s="4">
         <v>7633179</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C13" s="4">
         <v>2655478</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D13" s="4">
         <v>1991532</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E13" s="4">
         <v>1235548</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F13" s="4">
         <v>663641</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G13" s="4">
         <v>684771</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H13" s="4">
         <v>214168</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I13" s="4">
         <v>70671</v>
       </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="J13" s="1">
+        <v>116374</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>1983</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B14" s="4">
         <v>7730415</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C14" s="4">
         <v>2678250</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D14" s="4">
         <v>2012443</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E14" s="4">
         <v>1259140</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F14" s="4">
         <v>671738</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G14" s="4">
         <v>697570</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H14" s="4">
         <v>216145</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I14" s="4">
         <v>74225</v>
       </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="J14" s="1">
+        <v>119442</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
         <v>1984</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B15" s="4">
         <v>7826368</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C15" s="4">
         <v>2706580</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D15" s="4">
         <v>2033611</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E15" s="4">
         <v>1281035</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F15" s="4">
         <v>677950</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G15" s="4">
         <v>708066</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H15" s="4">
         <v>218417</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I15" s="4">
         <v>77307</v>
       </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="J15" s="1">
+        <v>122458</v>
+      </c>
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
         <v>1985</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B16" s="4">
         <v>7940033</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C16" s="4">
         <v>2739325</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D16" s="4">
         <v>2055418</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E16" s="4">
         <v>1306321</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F16" s="4">
         <v>684416</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G16" s="4">
         <v>724952</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H16" s="4">
         <v>220701</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I16" s="4">
         <v>80913</v>
       </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="J16" s="1">
+        <v>125549</v>
+      </c>
+      <c r="K16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
         <v>1986</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B17" s="4">
         <v>8057320</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C17" s="4">
         <v>2777230</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D17" s="4">
         <v>2076705</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E17" s="4">
         <v>1331718</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F17" s="4">
         <v>689991</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G17" s="4">
         <v>745203</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H17" s="4">
         <v>222486</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I17" s="4">
         <v>82828</v>
       </c>
-      <c r="J7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="J17" s="1">
+        <v>129616</v>
+      </c>
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
         <v>1987</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B18" s="4">
         <v>8181746</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C18" s="4">
         <v>2822255</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D18" s="4">
         <v>2102763</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E18" s="4">
         <v>1357083</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F18" s="4">
         <v>694962</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G18" s="4">
         <v>763238</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H18" s="4">
         <v>223099</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I18" s="4">
         <v>84054</v>
       </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="J18" s="1">
+        <v>132727</v>
+      </c>
+      <c r="K18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
         <v>1988</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B19" s="4">
         <v>8325068</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C19" s="4">
         <v>2865373</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D19" s="4">
         <v>2132228</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E19" s="4">
         <v>1394568</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F19" s="4">
         <v>701150</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G19" s="4">
         <v>785839</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H19" s="4">
         <v>224486</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I19" s="4">
         <v>84567</v>
       </c>
-      <c r="J9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="J19" s="1">
+        <v>135894</v>
+      </c>
+      <c r="K19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
         <v>1989</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B20" s="4">
         <v>8446656</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C20" s="4">
         <v>2889741</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D20" s="4">
         <v>2157614</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E20" s="4">
         <v>1435984</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F20" s="4">
         <v>707424</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G20" s="4">
         <v>803939</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H20" s="4">
         <v>227368</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I20" s="4">
         <v>85139</v>
       </c>
-      <c r="J10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="J20" s="1">
+        <v>138021</v>
+      </c>
+      <c r="K20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
         <v>1990</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B21" s="4">
         <v>8560533</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C21" s="4">
         <v>2918868</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D21" s="4">
         <v>2182990</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E21" s="4">
         <v>1468021</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F21" s="4">
         <v>713922</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G21" s="4">
         <v>817518</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H21" s="4">
         <v>230360</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I21" s="4">
         <v>86412</v>
       </c>
-      <c r="J11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="J21" s="1">
+        <v>141058</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
         <v>1991</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B22" s="4">
         <v>8659623</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C22" s="4">
         <v>2949765</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D22" s="4">
         <v>2198227</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E22" s="4">
         <v>1498387</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F22" s="4">
         <v>719693</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G22" s="4">
         <v>828333</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H22" s="4">
         <v>232161</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I22" s="4">
         <v>87447</v>
       </c>
-      <c r="J12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="J22" s="1">
+        <v>144636</v>
+      </c>
+      <c r="K22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
         <v>1992</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B23" s="4">
         <v>8744793</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C23" s="4">
         <v>2973116</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D23" s="4">
         <v>2207960</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E23" s="4">
         <v>1531688</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F23" s="4">
         <v>722422</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G23" s="4">
         <v>839016</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H23" s="4">
         <v>233344</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I23" s="4">
         <v>89336</v>
       </c>
-      <c r="J13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="J23" s="1">
+        <v>147218</v>
+      </c>
+      <c r="K23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>1993</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B24" s="4">
         <v>8821492</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C24" s="4">
         <v>2992409</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D24" s="4">
         <v>2210251</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E24" s="4">
         <v>1568796</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F24" s="4">
         <v>723824</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G24" s="4">
         <v>850115</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H24" s="4">
         <v>234016</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I24" s="4">
         <v>91059</v>
       </c>
-      <c r="J14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="J24" s="1">
+        <v>149428</v>
+      </c>
+      <c r="K24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>1994</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B25" s="4">
         <v>8906001</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C25" s="4">
         <v>3017659</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D25" s="4">
         <v>2217157</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E25" s="4">
         <v>1602949</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F25" s="4">
         <v>724614</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G25" s="4">
         <v>864237</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H25" s="4">
         <v>234310</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I25" s="4">
         <v>92782</v>
       </c>
-      <c r="J15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="J25" s="1">
+        <v>150330</v>
+      </c>
+      <c r="K25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
         <v>1995</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B26" s="4">
         <v>9014765</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C26" s="4">
         <v>3051661</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D26" s="4">
         <v>2232180</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E26" s="4">
         <v>1639626</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F26" s="4">
         <v>725527</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G26" s="4">
         <v>880875</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H26" s="4">
         <v>234726</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I26" s="4">
         <v>96094</v>
       </c>
-      <c r="J16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="J26" s="1">
+        <v>151968</v>
+      </c>
+      <c r="K26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
         <v>1996</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B27" s="4">
         <v>9112568</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C27" s="4">
         <v>3084364</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D27" s="4">
         <v>2247511</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E27" s="4">
         <v>1667529</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F27" s="4">
         <v>727752</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G27" s="4">
         <v>896354</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H27" s="4">
         <v>234801</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I27" s="4">
         <v>98533</v>
       </c>
-      <c r="J17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="J27" s="1">
+        <v>153635</v>
+      </c>
+      <c r="K27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
         <v>1997</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B28" s="4">
         <v>9195994</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C28" s="4">
         <v>3113586</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D28" s="4">
         <v>2261807</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E28" s="4">
         <v>1690173</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F28" s="4">
         <v>731108</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G28" s="4">
         <v>909323</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H28" s="4">
         <v>234121</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I28" s="4">
         <v>100542</v>
       </c>
-      <c r="J18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="J28" s="1">
+        <v>153940</v>
+      </c>
+      <c r="K28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
         <v>1998</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B29" s="4">
         <v>9288411</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C29" s="4">
         <v>3145134</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D29" s="4">
         <v>2281568</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E29" s="4">
         <v>1711755</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F29" s="4">
         <v>734801</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G29" s="4">
         <v>923208</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H29" s="4">
         <v>233581</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I29" s="4">
         <v>102153</v>
       </c>
-      <c r="J19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="J29" s="1">
+        <v>154547</v>
+      </c>
+      <c r="K29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
         <v>1999</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B30" s="4">
         <v>9390061</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C30" s="4">
         <v>3180554</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D30" s="4">
         <v>2304123</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E30" s="4">
         <v>1736360</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F30" s="4">
         <v>738697</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G30" s="4">
         <v>935454</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H30" s="4">
         <v>233321</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I30" s="4">
         <v>103992</v>
       </c>
-      <c r="J20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="J30" s="1">
+        <v>155599</v>
+      </c>
+      <c r="K30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
         <v>2000</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B31" s="4">
         <v>9496927</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C31" s="4">
         <v>3218964</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D31" s="4">
         <v>2329779</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E31" s="4">
         <v>1762325</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F31" s="4">
         <v>741358</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G31" s="4">
         <v>947617</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H31" s="4">
         <v>233190</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I31" s="4">
         <v>104802</v>
       </c>
-      <c r="J21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="J31" s="1">
+        <v>156815</v>
+      </c>
+      <c r="K31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
         <v>2001</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B32" s="4">
         <v>9618412</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C32" s="4">
         <v>3254898</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D32" s="4">
         <v>2359524</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E32" s="4">
         <v>1798645</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F32" s="4">
         <v>745132</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G32" s="4">
         <v>960276</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H32" s="4">
         <v>233538</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I32" s="4">
         <v>105795</v>
       </c>
-      <c r="J22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="J32" s="1">
+        <v>158666</v>
+      </c>
+      <c r="K32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>2002</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B33" s="4">
         <v>9729203</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C33" s="4">
         <v>3273797</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D33" s="4">
         <v>2388048</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E33" s="4">
         <v>1844415</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F33" s="4">
         <v>748889</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G33" s="4">
         <v>971887</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H33" s="4">
         <v>234542</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I33" s="4">
         <v>105552</v>
       </c>
-      <c r="J23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="J33" s="1">
+        <v>160138</v>
+      </c>
+      <c r="K33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>2003</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B34" s="4">
         <v>9842057</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C34" s="4">
         <v>3289793</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D34" s="4">
         <v>2417433</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E34" s="4">
         <v>1888810</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F34" s="4">
         <v>753182</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G34" s="4">
         <v>987320</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H34" s="4">
         <v>237271</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I34" s="4">
         <v>105230</v>
       </c>
-      <c r="J24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="J34" s="1">
+        <v>161568</v>
+      </c>
+      <c r="K34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>2004</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B35" s="4">
         <v>9952665</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C35" s="4">
         <v>3305332</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D35" s="4">
         <v>2447562</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E35" s="4">
         <v>1930447</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F35" s="4">
         <v>757014</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G35" s="4">
         <v>1003236</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H35" s="4">
         <v>239025</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I35" s="4">
         <v>106019</v>
       </c>
-      <c r="J25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="J35" s="1">
+        <v>162487</v>
+      </c>
+      <c r="K35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
         <v>2005</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B36" s="4">
         <v>10087382</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C36" s="4">
         <v>3327461</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D36" s="4">
         <v>2481962</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E36" s="4">
         <v>1977783</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F36" s="4">
         <v>762665</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G36" s="4">
         <v>1022918</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H36" s="4">
         <v>240625</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I36" s="4">
         <v>107839</v>
       </c>
-      <c r="J26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="J36" s="1">
+        <v>163832</v>
+      </c>
+      <c r="K36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>2006</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B37" s="4">
         <v>10248923</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C37" s="4">
         <v>3361292</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D37" s="4">
         <v>2524859</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E37" s="4">
         <v>2023921</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F37" s="4">
         <v>770847</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G37" s="4">
         <v>1047061</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H37" s="4">
         <v>242549</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I37" s="4">
         <v>109586</v>
       </c>
-      <c r="J27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="J37" s="1">
+        <v>165814</v>
+      </c>
+      <c r="K37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
         <v>2007</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B38" s="4">
         <v>10449776</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C38" s="4">
         <v>3413653</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D38" s="4">
         <v>2574619</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E38" s="4">
         <v>2076128</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F38" s="4">
         <v>779355</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G38" s="4">
         <v>1075987</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H38" s="4">
         <v>245319</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I38" s="4">
         <v>112777</v>
       </c>
-      <c r="J28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="J38" s="1">
+        <v>169640</v>
+      </c>
+      <c r="K38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
         <v>2008</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B39" s="4">
         <v>10689738</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C39" s="4">
         <v>3476199</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D39" s="4">
         <v>2633317</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E39" s="4">
         <v>2135996</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F39" s="4">
         <v>789696</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G39" s="4">
         <v>1113633</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H39" s="4">
         <v>248714</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I39" s="4">
         <v>116223</v>
       </c>
-      <c r="J29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="J39" s="1">
+        <v>172707</v>
+      </c>
+      <c r="K39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
         <v>2009</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B40" s="4">
         <v>10886022</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C40" s="4">
         <v>3526643</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D40" s="4">
         <v>2686022</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E40" s="4">
         <v>2181500</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F40" s="4">
         <v>800926</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G40" s="4">
         <v>1140480</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H40" s="4">
         <v>251434</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I40" s="4">
         <v>119297</v>
       </c>
-      <c r="J30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="J40" s="1">
+        <v>176325</v>
+      </c>
+      <c r="K40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
         <v>2010</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B41" s="4">
         <v>11034979</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C41" s="4">
         <v>3565558</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D41" s="4">
         <v>2720959</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E41" s="4">
         <v>2214429</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F41" s="4">
         <v>808037</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G41" s="4">
         <v>1167862</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H41" s="4">
         <v>253833</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I41" s="4">
         <v>120979</v>
       </c>
-      <c r="J31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="J41" s="1">
+        <v>179860</v>
+      </c>
+      <c r="K41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
         <v>2011</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B42" s="4">
         <v>11206252</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C42" s="4">
         <v>3604198</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D42" s="4">
         <v>2766513</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E42" s="4">
         <v>2253923</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F42" s="4">
         <v>815608</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G42" s="4">
         <v>1202068</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H42" s="4">
         <v>254814</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I42" s="4">
         <v>122136</v>
       </c>
-      <c r="J32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="J42" s="1">
+        <v>182996</v>
+      </c>
+      <c r="K42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
         <v>2012</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B43" s="4">
         <v>11408788</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C43" s="4">
         <v>3650035</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D43" s="4">
         <v>2825349</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E43" s="4">
         <v>2299776</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F43" s="4">
         <v>823688</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G43" s="4">
         <v>1239615</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H43" s="4">
         <v>254700</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I43" s="4">
         <v>125043</v>
       </c>
-      <c r="J33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="J43" s="1">
+        <v>187156</v>
+      </c>
+      <c r="K43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
         <v>2013</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B44" s="4">
         <v>11582448</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C44" s="4">
         <v>3698220</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D44" s="4">
         <v>2884387</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E44" s="4">
         <v>2333762</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F44" s="4">
         <v>830900</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G44" s="4">
         <v>1259941</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H44" s="4">
         <v>254878</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I44" s="4">
         <v>126854</v>
       </c>
-      <c r="J34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="J44" s="1">
+        <v>190367</v>
+      </c>
+      <c r="K44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
         <v>2014</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B45" s="4">
         <v>11744498</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C45" s="4">
         <v>3750061</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D45" s="4">
         <v>2945763</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E45" s="4">
         <v>2361282</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F45" s="4">
         <v>838094</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G45" s="4">
         <v>1271552</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H45" s="4">
         <v>254973</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I45" s="4">
         <v>126742</v>
       </c>
-      <c r="J35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="J45" s="1">
+        <v>192913</v>
+      </c>
+      <c r="K45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
         <v>2015</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B46" s="4">
         <v>11904308</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C46" s="4">
         <v>3803289</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D46" s="4">
         <v>3011376</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E46" s="4">
         <v>2385347</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F46" s="4">
         <v>843702</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G46" s="4">
         <v>1278792</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H46" s="4">
         <v>255452</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I46" s="4">
         <v>126967</v>
       </c>
-      <c r="J36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="J46" s="1">
+        <v>196237</v>
+      </c>
+      <c r="K46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
         <v>2016</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B47" s="4">
         <v>12098143</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C47" s="4">
         <v>3865361</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D47" s="4">
         <v>3082379</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E47" s="4">
         <v>2421215</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F47" s="4">
         <v>849914</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G47" s="4">
         <v>1288303</v>
       </c>
-      <c r="H37" s="4">
+      <c r="H47" s="4">
         <v>258456</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I47" s="4">
         <v>127526</v>
       </c>
-      <c r="J37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="J47" s="1">
+        <v>199780</v>
+      </c>
+      <c r="K47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
         <v>2017</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B48" s="4">
         <v>12284961</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C48" s="4">
         <v>3921301</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D48" s="4">
         <v>3144429</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E48" s="4">
         <v>2458389</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F48" s="4">
         <v>857807</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G48" s="4">
         <v>1302076</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H48" s="4">
         <v>263305</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I48" s="4">
         <v>127285</v>
       </c>
-      <c r="J38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="J48" s="1">
+        <v>205448</v>
+      </c>
+      <c r="K48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
         <v>2018</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B49" s="4">
         <v>12481024</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C49" s="4">
         <v>3976266</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D49" s="4">
         <v>3207192</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E49" s="4">
         <v>2499842</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F49" s="4">
         <v>867603</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G49" s="4">
         <v>1319834</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H49" s="4">
         <v>268840</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I49" s="4">
         <v>126108</v>
       </c>
-      <c r="J39" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="J49" s="1">
+        <v>210616</v>
+      </c>
+      <c r="K49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
         <v>2019</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B50" s="4">
         <v>12665662</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C50" s="4">
         <v>4019498</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D50" s="4">
         <v>3262240</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E50" s="4">
         <v>2540680</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F50" s="4">
         <v>878768</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G50" s="4">
         <v>1345064</v>
       </c>
-      <c r="H40" s="4">
+      <c r="H50" s="4">
         <v>273893</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I50" s="4">
         <v>125486</v>
       </c>
-      <c r="J40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="J50" s="1">
+        <v>215222</v>
+      </c>
+      <c r="K50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
         <v>2020</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B51" s="4">
         <v>12718550</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C51" s="4">
         <v>4022460</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D51" s="4">
         <v>3248276</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E51" s="4">
         <v>2568499</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F51" s="4">
         <v>886475</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G51" s="4">
         <v>1364994</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H51" s="4">
         <v>278353</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I51" s="4">
         <v>126047</v>
       </c>
-      <c r="J41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="J51" s="1">
+        <v>219576</v>
+      </c>
+      <c r="K51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
         <v>2021</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B52" s="4">
         <v>12794464</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C52" s="4">
         <v>4035537</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D52" s="4">
         <v>3240587</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E52" s="4">
         <v>2601798</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F52" s="4">
         <v>893667</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G52" s="4">
         <v>1384481</v>
       </c>
-      <c r="H42" s="4">
+      <c r="H52" s="4">
         <v>282872</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I52" s="4">
         <v>127693</v>
       </c>
-      <c r="J42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+      <c r="J52" s="1">
+        <v>223361</v>
+      </c>
+      <c r="K52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
         <v>2022</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B53" s="4">
         <v>13065824</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C53" s="4">
         <v>4110669</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D53" s="4">
         <v>3310463</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E53" s="4">
         <v>2662454</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F53" s="4">
         <v>910235</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G53" s="4">
         <v>1424238</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H53" s="4">
         <v>284586</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I53" s="4">
         <v>130444</v>
       </c>
-      <c r="J43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="J53" s="1">
+        <v>225594</v>
+      </c>
+      <c r="K53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
         <v>2023</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B54" s="4">
         <v>13386814</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C54" s="4">
         <v>4198713</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D54" s="4">
         <v>3399523</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E54" s="4">
         <v>2732292</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F54" s="4">
         <v>925497</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G54" s="4">
         <v>1476429</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H54" s="4">
         <v>284789</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I54" s="4">
         <v>132950</v>
       </c>
-      <c r="J44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="J54" s="1">
+        <v>229413</v>
+      </c>
+      <c r="K54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
         <v>2024</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B55" s="4">
         <v>13599086</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C55" s="4">
         <v>4249320</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D55" s="4">
         <v>3458551</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E55" s="4">
         <v>2782663</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F55" s="4">
         <v>935554</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G55" s="4">
         <v>1513739</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H55" s="4">
         <v>285384</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I55" s="4">
         <v>134925</v>
       </c>
-      <c r="J45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="J55" s="1">
+        <v>233792</v>
+      </c>
+      <c r="K55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
         <v>2025</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B56" s="4">
         <v>13671065</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C56" s="4">
         <v>4268307</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D56" s="4">
         <v>3480553</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E56" s="4">
         <v>2797120</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F56" s="4">
         <v>939246</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G56" s="4">
         <v>1524684</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H56" s="4">
         <v>285638</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I56" s="4">
         <v>135618</v>
       </c>
-      <c r="J46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
+      <c r="J56" s="1">
+        <v>238565</v>
+      </c>
+      <c r="K56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1971</v>
+      </c>
+      <c r="B57" s="1">
+        <v>6499329</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2351719</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1801866</v>
+      </c>
+      <c r="E57" s="1">
+        <v>918509</v>
+      </c>
+      <c r="F57" s="1">
+        <v>602542</v>
+      </c>
+      <c r="G57" s="1">
+        <v>514502</v>
+      </c>
+      <c r="H57" s="1">
+        <v>198158</v>
+      </c>
+      <c r="I57" s="1">
+        <v>37985</v>
+      </c>
+      <c r="J57" s="1">
+        <v>74048</v>
+      </c>
+      <c r="K57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1972</v>
+      </c>
+      <c r="B58" s="1">
+        <v>6618511</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2387394</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1832276</v>
+      </c>
+      <c r="E58" s="1">
+        <v>941519</v>
+      </c>
+      <c r="F58" s="1">
+        <v>609574</v>
+      </c>
+      <c r="G58" s="1">
+        <v>528872</v>
+      </c>
+      <c r="H58" s="1">
+        <v>199382</v>
+      </c>
+      <c r="I58" s="1">
+        <v>41211</v>
+      </c>
+      <c r="J58" s="1">
+        <v>78283</v>
+      </c>
+      <c r="K58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1973</v>
+      </c>
+      <c r="B59" s="1">
+        <v>6721690</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2413371</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1855597</v>
+      </c>
+      <c r="E59" s="1">
+        <v>967870</v>
+      </c>
+      <c r="F59" s="1">
+        <v>616406</v>
+      </c>
+      <c r="G59" s="1">
+        <v>538783</v>
+      </c>
+      <c r="H59" s="1">
+        <v>200968</v>
+      </c>
+      <c r="I59" s="1">
+        <v>43877</v>
+      </c>
+      <c r="J59" s="1">
+        <v>84818</v>
+      </c>
+      <c r="K59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1974</v>
+      </c>
+      <c r="B60" s="1">
+        <v>6832903</v>
+      </c>
+      <c r="C60" s="1">
+        <v>2441635</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1879906</v>
+      </c>
+      <c r="E60" s="1">
+        <v>995692</v>
+      </c>
+      <c r="F60" s="1">
+        <v>622676</v>
+      </c>
+      <c r="G60" s="1">
+        <v>552168</v>
+      </c>
+      <c r="H60" s="1">
+        <v>202734</v>
+      </c>
+      <c r="I60" s="1">
+        <v>46879</v>
+      </c>
+      <c r="J60" s="1">
+        <v>91213</v>
+      </c>
+      <c r="K60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1975</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6923814</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2464232</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1896942</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1017665</v>
+      </c>
+      <c r="F61" s="1">
+        <v>634769</v>
+      </c>
+      <c r="G61" s="1">
+        <v>566319</v>
+      </c>
+      <c r="H61" s="1">
+        <v>204823</v>
+      </c>
+      <c r="I61" s="1">
+        <v>41388</v>
+      </c>
+      <c r="J61" s="1">
+        <v>97676</v>
+      </c>
+      <c r="K61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1976</v>
+      </c>
+      <c r="B62" s="1">
+        <v>7001049</v>
+      </c>
+      <c r="C62" s="1">
+        <v>2482610</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1909938</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1038840</v>
+      </c>
+      <c r="F62" s="1">
+        <v>638918</v>
+      </c>
+      <c r="G62" s="1">
+        <v>578383</v>
+      </c>
+      <c r="H62" s="1">
+        <v>206121</v>
+      </c>
+      <c r="I62" s="1">
+        <v>44132</v>
+      </c>
+      <c r="J62" s="1">
+        <v>102107</v>
+      </c>
+      <c r="K62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1977</v>
+      </c>
+      <c r="B63" s="1">
+        <v>7087532</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2505790</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1925464</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1058544</v>
+      </c>
+      <c r="F63" s="1">
+        <v>645573</v>
+      </c>
+      <c r="G63" s="1">
+        <v>592221</v>
+      </c>
+      <c r="H63" s="1">
+        <v>207487</v>
+      </c>
+      <c r="I63" s="1">
+        <v>47110</v>
+      </c>
+      <c r="J63" s="1">
+        <v>105343</v>
+      </c>
+      <c r="K63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1978</v>
+      </c>
+      <c r="B64" s="1">
+        <v>7177962</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2534006</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1940829</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1080465</v>
+      </c>
+      <c r="F64" s="1">
+        <v>651494</v>
+      </c>
+      <c r="G64" s="1">
+        <v>604589</v>
+      </c>
+      <c r="H64" s="1">
+        <v>208783</v>
+      </c>
+      <c r="I64" s="1">
+        <v>49975</v>
+      </c>
+      <c r="J64" s="1">
+        <v>107821</v>
+      </c>
+      <c r="K64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1979</v>
+      </c>
+      <c r="B65" s="1">
+        <v>7261967</v>
+      </c>
+      <c r="C65" s="1">
+        <v>2564256</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1954074</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1101997</v>
+      </c>
+      <c r="F65" s="1">
+        <v>654860</v>
+      </c>
+      <c r="G65" s="1">
+        <v>614579</v>
+      </c>
+      <c r="H65" s="1">
+        <v>210442</v>
+      </c>
+      <c r="I65" s="1">
+        <v>52158</v>
+      </c>
+      <c r="J65" s="1">
+        <v>109601</v>
+      </c>
+      <c r="K65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1980</v>
+      </c>
+      <c r="B66" s="1">
+        <v>7357296</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2594910</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1969903</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1127638</v>
+      </c>
+      <c r="F66" s="1">
+        <v>658176</v>
+      </c>
+      <c r="G66" s="1">
+        <v>627133</v>
+      </c>
+      <c r="H66" s="1">
+        <v>212590</v>
+      </c>
+      <c r="I66" s="1">
+        <v>55026</v>
+      </c>
+      <c r="J66" s="1">
+        <v>111920</v>
+      </c>
+      <c r="K66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>1981</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B67" s="6">
         <v>7539778</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C67" s="6">
         <v>2642315</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D67" s="6">
         <v>1999049</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E67" s="6">
         <v>1187439</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F67" s="6">
         <v>668162</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G67" s="6">
         <v>652840</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H67" s="6">
         <v>215348</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I67" s="6">
         <v>59695</v>
       </c>
-      <c r="J47" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="J67" s="1">
+        <v>113976</v>
+      </c>
+      <c r="K67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
         <v>1982</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B68" s="6">
         <v>7655712</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C68" s="6">
         <v>2672743</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D68" s="6">
         <v>2021155</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E68" s="6">
         <v>1220927</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F68" s="6">
         <v>674142</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G68" s="6">
         <v>670200</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H68" s="6">
         <v>216806</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I68" s="6">
         <v>62113</v>
       </c>
-      <c r="J48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="J68" s="1">
+        <v>116671</v>
+      </c>
+      <c r="K68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
         <v>1983</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B69" s="6">
         <v>7753081</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C69" s="6">
         <v>2696665</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D69" s="6">
         <v>2042055</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E69" s="6">
         <v>1244145</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F69" s="6">
         <v>681470</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G69" s="6">
         <v>683441</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H69" s="6">
         <v>218955</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I69" s="6">
         <v>65294</v>
       </c>
-      <c r="J49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="J69" s="1">
+        <v>119541</v>
+      </c>
+      <c r="K69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
         <v>1984</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B70" s="6">
         <v>7850914</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C70" s="6">
         <v>2725172</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D70" s="6">
         <v>2064029</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E70" s="6">
         <v>1266043</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F70" s="6">
         <v>687383</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G70" s="6">
         <v>694966</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H70" s="6">
         <v>221653</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I70" s="6">
         <v>67986</v>
       </c>
-      <c r="J50" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="J70" s="1">
+        <v>122654</v>
+      </c>
+      <c r="K70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
         <v>1985</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B71" s="6">
         <v>7960533</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C71" s="6">
         <v>2757142</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D71" s="6">
         <v>2085003</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E71" s="6">
         <v>1290779</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F71" s="6">
         <v>692422</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G71" s="6">
         <v>711948</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H71" s="6">
         <v>223875</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I71" s="6">
         <v>71443</v>
       </c>
-      <c r="J51" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="J71" s="1">
+        <v>125840</v>
+      </c>
+      <c r="K71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
         <v>1986</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B72" s="6">
         <v>8081449</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C72" s="6">
         <v>2797021</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D72" s="6">
         <v>2107137</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E72" s="6">
         <v>1317060</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F72" s="6">
         <v>697508</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G72" s="6">
         <v>732195</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H72" s="6">
         <v>225749</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I72" s="6">
         <v>73750</v>
       </c>
-      <c r="J52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="J72" s="1">
+        <v>129294</v>
+      </c>
+      <c r="K72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
         <v>1987</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B73" s="6">
         <v>8212895</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C73" s="6">
         <v>2843964</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D73" s="6">
         <v>2132182</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E73" s="6">
         <v>1346433</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F73" s="6">
         <v>703997</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G73" s="6">
         <v>750117</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H73" s="6">
         <v>226721</v>
       </c>
-      <c r="I53" s="6">
+      <c r="I73" s="6">
         <v>74986</v>
       </c>
-      <c r="J53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="J73" s="1">
+        <v>132750</v>
+      </c>
+      <c r="K73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
         <v>1988</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B74" s="6">
         <v>8362014</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C74" s="6">
         <v>2886881</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D74" s="6">
         <v>2163072</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E74" s="6">
         <v>1386301</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F74" s="6">
         <v>711173</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G74" s="6">
         <v>773075</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H74" s="6">
         <v>228295</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I74" s="6">
         <v>75969</v>
       </c>
-      <c r="J54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="J74" s="1">
+        <v>136235</v>
+      </c>
+      <c r="K74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
         <v>1989</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B75" s="6">
         <v>8490067</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C75" s="6">
         <v>2913338</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D75" s="6">
         <v>2190611</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E75" s="6">
         <v>1428023</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F75" s="6">
         <v>718037</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G75" s="6">
         <v>792286</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H75" s="6">
         <v>231042</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I75" s="6">
         <v>76958</v>
       </c>
-      <c r="J55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="J75" s="1">
+        <v>138411</v>
+      </c>
+      <c r="K75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
         <v>1990</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B76" s="6">
         <v>8609235</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C76" s="6">
         <v>2943629</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D76" s="6">
         <v>2217717</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E76" s="6">
         <v>1460692</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F76" s="6">
         <v>724960</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G76" s="6">
         <v>806872</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H76" s="6">
         <v>234160</v>
       </c>
-      <c r="I56" s="6">
+      <c r="I76" s="6">
         <v>78635</v>
       </c>
-      <c r="J56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="J76" s="1">
+        <v>141153</v>
+      </c>
+      <c r="K76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
         <v>1991</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B77" s="6">
         <v>8719358</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C77" s="6">
         <v>2978307</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D77" s="6">
         <v>2236856</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E77" s="6">
         <v>1492054</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F77" s="6">
         <v>731169</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G77" s="6">
         <v>819075</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H77" s="6">
         <v>236388</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I77" s="6">
         <v>79596</v>
       </c>
-      <c r="J57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="J77" s="1">
+        <v>144684</v>
+      </c>
+      <c r="K77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
         <v>1992</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B78" s="6">
         <v>8812340</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C78" s="6">
         <v>3004707</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D78" s="6">
         <v>2250259</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E78" s="6">
         <v>1525450</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F78" s="6">
         <v>734819</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G78" s="6">
         <v>829499</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H78" s="6">
         <v>237914</v>
       </c>
-      <c r="I58" s="6">
+      <c r="I78" s="6">
         <v>81084</v>
       </c>
-      <c r="J58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="J78" s="1">
+        <v>147669</v>
+      </c>
+      <c r="K78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
         <v>1993</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B79" s="6">
         <v>8897598</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C79" s="6">
         <v>3027762</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D79" s="6">
         <v>2256487</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E79" s="6">
         <v>1562190</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F79" s="6">
         <v>737278</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G79" s="6">
         <v>840233</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H79" s="6">
         <v>238967</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I79" s="6">
         <v>82531</v>
       </c>
-      <c r="J59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="J79" s="1">
+        <v>150325</v>
+      </c>
+      <c r="K79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
         <v>1994</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B80" s="6">
         <v>8987432</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C80" s="6">
         <v>3054213</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D80" s="6">
         <v>2266048</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E80" s="6">
         <v>1595928</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F80" s="6">
         <v>739363</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G80" s="6">
         <v>854312</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H80" s="6">
         <v>239766</v>
       </c>
-      <c r="I60" s="6">
+      <c r="I80" s="6">
         <v>83979</v>
       </c>
-      <c r="J60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="J80" s="1">
+        <v>151864</v>
+      </c>
+      <c r="K80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
         <v>1995</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B81" s="6">
         <v>9104851</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C81" s="6">
         <v>3092310</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D81" s="6">
         <v>2285173</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E81" s="6">
         <v>1632117</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F81" s="6">
         <v>741078</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G81" s="6">
         <v>871058</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H81" s="6">
         <v>240422</v>
       </c>
-      <c r="I61" s="6">
+      <c r="I81" s="6">
         <v>86735</v>
       </c>
-      <c r="J61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+      <c r="J81" s="1">
+        <v>153870</v>
+      </c>
+      <c r="K81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
         <v>1996</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B82" s="6">
         <v>9217511</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C82" s="6">
         <v>3130184</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D82" s="6">
         <v>2305393</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E82" s="6">
         <v>1663050</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F82" s="6">
         <v>744245</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G82" s="6">
         <v>887202</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H82" s="6">
         <v>240728</v>
       </c>
-      <c r="I62" s="6">
+      <c r="I82" s="6">
         <v>88809</v>
       </c>
-      <c r="J62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+      <c r="J82" s="1">
+        <v>155994</v>
+      </c>
+      <c r="K82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
         <v>1997</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B83" s="6">
         <v>9314010</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C83" s="6">
         <v>3161380</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D83" s="6">
         <v>2324349</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E83" s="6">
         <v>1690221</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F83" s="6">
         <v>747895</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G83" s="6">
         <v>901605</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H83" s="6">
         <v>240094</v>
       </c>
-      <c r="I63" s="6">
+      <c r="I83" s="6">
         <v>90717</v>
       </c>
-      <c r="J63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+      <c r="J83" s="1">
+        <v>156593</v>
+      </c>
+      <c r="K83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
         <v>1998</v>
       </c>
-      <c r="B64" s="6">
+      <c r="B84" s="6">
         <v>9417209</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C84" s="6">
         <v>3193656</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D84" s="6">
         <v>2347777</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E84" s="6">
         <v>1715750</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F84" s="6">
         <v>752241</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G84" s="6">
         <v>916870</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H84" s="6">
         <v>239869</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I84" s="6">
         <v>92237</v>
       </c>
-      <c r="J64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+      <c r="J84" s="1">
+        <v>156985</v>
+      </c>
+      <c r="K84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
         <v>1999</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B85" s="6">
         <v>9529149</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C85" s="6">
         <v>3229417</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D85" s="6">
         <v>2373458</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E85" s="6">
         <v>1744674</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F85" s="6">
         <v>756521</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G85" s="6">
         <v>930811</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H85" s="6">
         <v>239973</v>
       </c>
-      <c r="I65" s="6">
+      <c r="I85" s="6">
         <v>93765</v>
       </c>
-      <c r="J65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+      <c r="J85" s="1">
+        <v>158572</v>
+      </c>
+      <c r="K85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
         <v>2000</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B86" s="6">
         <v>9644109</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C86" s="6">
         <v>3266117</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D86" s="6">
         <v>2401076</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E86" s="6">
         <v>1775345</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F86" s="6">
         <v>758771</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G86" s="6">
         <v>944914</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H86" s="6">
         <v>240010</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I86" s="6">
         <v>95243</v>
       </c>
-      <c r="J66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+      <c r="J86" s="1">
+        <v>160420</v>
+      </c>
+      <c r="K86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
         <v>2001</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B87" s="6">
         <v>9768049</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C87" s="6">
         <v>3303586</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D87" s="6">
         <v>2430688</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E87" s="6">
         <v>1812558</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F87" s="6">
         <v>762693</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G87" s="6">
         <v>957476</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H87" s="6">
         <v>240352</v>
       </c>
-      <c r="I67" s="6">
+      <c r="I87" s="6">
         <v>95956</v>
       </c>
-      <c r="J67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+      <c r="J87" s="1">
+        <v>162872</v>
+      </c>
+      <c r="K87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
         <v>2002</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B88" s="6">
         <v>9876238</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C88" s="6">
         <v>3325644</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D88" s="6">
         <v>2456976</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E88" s="6">
         <v>1856376</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F88" s="6">
         <v>766834</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G88" s="6">
         <v>966723</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H88" s="6">
         <v>241456</v>
       </c>
-      <c r="I68" s="6">
+      <c r="I88" s="6">
         <v>95997</v>
       </c>
-      <c r="J68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+      <c r="J88" s="1">
+        <v>164489</v>
+      </c>
+      <c r="K88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
         <v>2003</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B89" s="6">
         <v>9985098</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C89" s="6">
         <v>3344716</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D89" s="6">
         <v>2482743</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E89" s="6">
         <v>1899750</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F89" s="6">
         <v>771545</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G89" s="6">
         <v>978810</v>
       </c>
-      <c r="H69" s="6">
+      <c r="H89" s="6">
         <v>244140</v>
       </c>
-      <c r="I69" s="6">
+      <c r="I89" s="6">
         <v>96478</v>
       </c>
-      <c r="J69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+      <c r="J89" s="1">
+        <v>165789</v>
+      </c>
+      <c r="K89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
         <v>2004</v>
       </c>
-      <c r="B70" s="6">
+      <c r="B90" s="6">
         <v>10093338</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C90" s="6">
         <v>3363874</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D90" s="6">
         <v>2509585</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E90" s="6">
         <v>1941904</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F90" s="6">
         <v>775548</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G90" s="6">
         <v>991005</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H90" s="6">
         <v>245753</v>
       </c>
-      <c r="I70" s="6">
+      <c r="I90" s="6">
         <v>97838</v>
       </c>
-      <c r="J70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+      <c r="J90" s="1">
+        <v>166453</v>
+      </c>
+      <c r="K90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
         <v>2005</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B91" s="6">
         <v>10224161</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C91" s="6">
         <v>3390562</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D91" s="6">
         <v>2541241</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E91" s="6">
         <v>1986392</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F91" s="6">
         <v>782187</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G91" s="6">
         <v>1007018</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H91" s="6">
         <v>247473</v>
       </c>
-      <c r="I71" s="6">
+      <c r="I91" s="6">
         <v>99546</v>
       </c>
-      <c r="J71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+      <c r="J91" s="1">
+        <v>167567</v>
+      </c>
+      <c r="K91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
         <v>2006</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B92" s="6">
         <v>10378624</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C92" s="6">
         <v>3424868</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D92" s="6">
         <v>2579106</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E92" s="6">
         <v>2031924</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F92" s="6">
         <v>790453</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G92" s="6">
         <v>1029806</v>
       </c>
-      <c r="H72" s="6">
+      <c r="H92" s="6">
         <v>248966</v>
       </c>
-      <c r="I72" s="6">
+      <c r="I92" s="6">
         <v>101443</v>
       </c>
-      <c r="J72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+      <c r="J92" s="1">
+        <v>169356</v>
+      </c>
+      <c r="K92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
         <v>2007</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B93" s="6">
         <v>10566345</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C93" s="6">
         <v>3470199</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D93" s="6">
         <v>2624884</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E93" s="6">
         <v>2083862</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F93" s="6">
         <v>799134</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G93" s="6">
         <v>1059019</v>
       </c>
-      <c r="H73" s="6">
+      <c r="H93" s="6">
         <v>250539</v>
       </c>
-      <c r="I73" s="6">
+      <c r="I93" s="6">
         <v>103841</v>
       </c>
-      <c r="J73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+      <c r="J93" s="1">
+        <v>173004</v>
+      </c>
+      <c r="K93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
         <v>2008</v>
       </c>
-      <c r="B74" s="6">
+      <c r="B94" s="6">
         <v>10785887</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C94" s="6">
         <v>3525583</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D94" s="6">
         <v>2679968</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E94" s="6">
         <v>2139555</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F94" s="6">
         <v>808184</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G94" s="6">
         <v>1095295</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H94" s="6">
         <v>253060</v>
       </c>
-      <c r="I74" s="6">
+      <c r="I94" s="6">
         <v>106303</v>
       </c>
-      <c r="J74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+      <c r="J94" s="1">
+        <v>175661</v>
+      </c>
+      <c r="K94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
         <v>2009</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B95" s="6">
         <v>10979601</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C95" s="6">
         <v>3574861</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D95" s="6">
         <v>2733227</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E95" s="6">
         <v>2185954</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F95" s="6">
         <v>817652</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G95" s="6">
         <v>1123267</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H95" s="6">
         <v>255027</v>
       </c>
-      <c r="I75" s="6">
+      <c r="I95" s="6">
         <v>108486</v>
       </c>
-      <c r="J75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+      <c r="J95" s="1">
+        <v>178460</v>
+      </c>
+      <c r="K95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
         <v>2010</v>
       </c>
-      <c r="B76" s="6">
+      <c r="B96" s="6">
         <v>11137490</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C96" s="6">
         <v>3614333</v>
       </c>
-      <c r="D76" s="6">
+      <c r="D96" s="6">
         <v>2774752</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E96" s="6">
         <v>2222453</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F96" s="6">
         <v>824445</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G96" s="6">
         <v>1151201</v>
       </c>
-      <c r="H76" s="6">
+      <c r="H96" s="6">
         <v>256386</v>
       </c>
-      <c r="I76" s="6">
+      <c r="I96" s="6">
         <v>109320</v>
       </c>
-      <c r="J76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+      <c r="J96" s="1">
+        <v>181906</v>
+      </c>
+      <c r="K96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
         <v>2011</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B97" s="6">
         <v>11315945</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C97" s="6">
         <v>3654524</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D97" s="6">
         <v>2825305</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E97" s="6">
         <v>2264726</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F97" s="6">
         <v>831575</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G97" s="6">
         <v>1183879</v>
       </c>
-      <c r="H77" s="6">
+      <c r="H97" s="6">
         <v>256925</v>
       </c>
-      <c r="I77" s="6">
+      <c r="I97" s="6">
         <v>110816</v>
       </c>
-      <c r="J77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+      <c r="J97" s="1">
+        <v>184989</v>
+      </c>
+      <c r="K97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
         <v>2012</v>
       </c>
-      <c r="B78" s="6">
+      <c r="B98" s="6">
         <v>11519235</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C98" s="6">
         <v>3703154</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D98" s="6">
         <v>2884237</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E98" s="6">
         <v>2311528</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F98" s="6">
         <v>839394</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G98" s="6">
         <v>1217874</v>
       </c>
-      <c r="H78" s="6">
+      <c r="H98" s="6">
         <v>257113</v>
       </c>
-      <c r="I78" s="6">
+      <c r="I98" s="6">
         <v>113685</v>
       </c>
-      <c r="J78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+      <c r="J98" s="1">
+        <v>189383</v>
+      </c>
+      <c r="K98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
         <v>2013</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B99" s="6">
         <v>11715329</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C99" s="6">
         <v>3756718</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D99" s="6">
         <v>2948198</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E99" s="6">
         <v>2351677</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F99" s="6">
         <v>847152</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G99" s="6">
         <v>1242247</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H99" s="6">
         <v>258137</v>
       </c>
-      <c r="I79" s="6">
+      <c r="I99" s="6">
         <v>115450</v>
       </c>
-      <c r="J79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+      <c r="J99" s="1">
+        <v>192890</v>
+      </c>
+      <c r="K99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
         <v>2014</v>
       </c>
-      <c r="B80" s="6">
+      <c r="B100" s="6">
         <v>11895833</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C100" s="6">
         <v>3812110</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D100" s="6">
         <v>3011749</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E100" s="6">
         <v>2385981</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F100" s="6">
         <v>855013</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G100" s="6">
         <v>1257067</v>
       </c>
-      <c r="H80" s="6">
+      <c r="H100" s="6">
         <v>259067</v>
       </c>
-      <c r="I80" s="6">
+      <c r="I100" s="6">
         <v>116011</v>
       </c>
-      <c r="J80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+      <c r="J100" s="1">
+        <v>195886</v>
+      </c>
+      <c r="K100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
         <v>2015</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B101" s="6">
         <v>12080273</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C101" s="6">
         <v>3868112</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D101" s="6">
         <v>3081673</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E101" s="6">
         <v>2419586</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F101" s="6">
         <v>862235</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G101" s="6">
         <v>1268953</v>
       </c>
-      <c r="H81" s="6">
+      <c r="H101" s="6">
         <v>260242</v>
       </c>
-      <c r="I81" s="6">
+      <c r="I101" s="6">
         <v>117123</v>
       </c>
-      <c r="J81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+      <c r="J101" s="1">
+        <v>199576</v>
+      </c>
+      <c r="K101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
         <v>2016</v>
       </c>
-      <c r="B82" s="6">
+      <c r="B102" s="6">
         <v>12286921</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C102" s="6">
         <v>3930264</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D102" s="6">
         <v>3153402</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E102" s="6">
         <v>2461724</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F102" s="6">
         <v>869666</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G102" s="6">
         <v>1281303</v>
       </c>
-      <c r="H82" s="6">
+      <c r="H102" s="6">
         <v>263525</v>
       </c>
-      <c r="I82" s="6">
+      <c r="I102" s="6">
         <v>118539</v>
       </c>
-      <c r="J82" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+      <c r="J102" s="1">
+        <v>203324</v>
+      </c>
+      <c r="K102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
         <v>2017</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B103" s="6">
         <v>12474057</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C103" s="6">
         <v>3979645</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D103" s="6">
         <v>3213781</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E103" s="6">
         <v>2502576</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F103" s="6">
         <v>877847</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G103" s="6">
         <v>1297852</v>
       </c>
-      <c r="H83" s="6">
+      <c r="H103" s="6">
         <v>268256</v>
       </c>
-      <c r="I83" s="6">
+      <c r="I103" s="6">
         <v>119577</v>
       </c>
-      <c r="J83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+      <c r="J103" s="1">
+        <v>209598</v>
+      </c>
+      <c r="K103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
         <v>2018</v>
       </c>
-      <c r="B84" s="6">
+      <c r="B104" s="6">
         <v>12665116</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C104" s="6">
         <v>4027298</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D104" s="6">
         <v>3272503</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E104" s="6">
         <v>2546592</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F104" s="6">
         <v>888112</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G104" s="6">
         <v>1316570</v>
       </c>
-      <c r="H84" s="6">
+      <c r="H104" s="6">
         <v>274087</v>
       </c>
-      <c r="I84" s="6">
+      <c r="I104" s="6">
         <v>119812</v>
       </c>
-      <c r="J84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
+      <c r="J104" s="1">
+        <v>215465</v>
+      </c>
+      <c r="K104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
         <v>2019</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B105" s="6">
         <v>12854806</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C105" s="6">
         <v>4068863</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D105" s="6">
         <v>3327810</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E105" s="6">
         <v>2589061</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F105" s="6">
         <v>900160</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G105" s="6">
         <v>1343735</v>
       </c>
-      <c r="H85" s="6">
+      <c r="H105" s="6">
         <v>279447</v>
       </c>
-      <c r="I85" s="6">
+      <c r="I105" s="6">
         <v>120727</v>
       </c>
-      <c r="J85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
+      <c r="J105" s="1">
+        <v>220508</v>
+      </c>
+      <c r="K105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
         <v>2020</v>
       </c>
-      <c r="B86" s="6">
+      <c r="B106" s="6">
         <v>12912148</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C106" s="6">
         <v>4071840</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D106" s="6">
         <v>3318919</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E106" s="6">
         <v>2615830</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F106" s="6">
         <v>908039</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G106" s="6">
         <v>1363193</v>
       </c>
-      <c r="H86" s="6">
+      <c r="H106" s="6">
         <v>283528</v>
       </c>
-      <c r="I86" s="6">
+      <c r="I106" s="6">
         <v>121772</v>
       </c>
-      <c r="J86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+      <c r="J106" s="1">
+        <v>225327</v>
+      </c>
+      <c r="K106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
         <v>2021</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B107" s="6">
         <v>12979331</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C107" s="6">
         <v>4081520</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D107" s="6">
         <v>3314426</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E107" s="6">
         <v>2647874</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F107" s="6">
         <v>914172</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G107" s="6">
         <v>1378759</v>
       </c>
-      <c r="H87" s="6">
+      <c r="H107" s="6">
         <v>286737</v>
       </c>
-      <c r="I87" s="6">
+      <c r="I107" s="6">
         <v>122807</v>
       </c>
-      <c r="J87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+      <c r="J107" s="1">
+        <v>229147</v>
+      </c>
+      <c r="K107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
         <v>2022</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B108" s="6">
         <v>13254461</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C108" s="6">
         <v>4153379</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D108" s="6">
         <v>3389932</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E108" s="6">
         <v>2714224</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F108" s="6">
         <v>929952</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G108" s="6">
         <v>1415285</v>
       </c>
-      <c r="H88" s="6">
+      <c r="H108" s="6">
         <v>288757</v>
       </c>
-      <c r="I88" s="6">
+      <c r="I108" s="6">
         <v>124850</v>
       </c>
-      <c r="J88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+      <c r="J108" s="1">
+        <v>231295</v>
+      </c>
+      <c r="K108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
         <v>2023</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B109" s="6">
         <v>13569846</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C109" s="6">
         <v>4238621</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D109" s="6">
         <v>3481545</v>
       </c>
-      <c r="E89" s="6">
+      <c r="E109" s="6">
         <v>2784184</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F109" s="6">
         <v>945440</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G109" s="6">
         <v>1461218</v>
       </c>
-      <c r="H89" s="6">
+      <c r="H109" s="6">
         <v>289425</v>
       </c>
-      <c r="I89" s="6">
+      <c r="I109" s="6">
         <v>126193</v>
       </c>
-      <c r="J89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
+      <c r="J109" s="1">
+        <v>235558</v>
+      </c>
+      <c r="K109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
         <v>2024</v>
       </c>
-      <c r="B90" s="6">
+      <c r="B110" s="6">
         <v>13793550</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C110" s="6">
         <v>4291866</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D110" s="6">
         <v>3549099</v>
       </c>
-      <c r="E90" s="6">
+      <c r="E110" s="6">
         <v>2836396</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F110" s="6">
         <v>955716</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G110" s="6">
         <v>1495660</v>
       </c>
-      <c r="H90" s="6">
+      <c r="H110" s="6">
         <v>290097</v>
       </c>
-      <c r="I90" s="6">
+      <c r="I110" s="6">
         <v>127329</v>
       </c>
-      <c r="J90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="7">
+      <c r="J110" s="1">
+        <v>240307</v>
+      </c>
+      <c r="K110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111">
         <v>2025</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B111" s="6">
         <v>13865809</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C111" s="6">
         <v>4310912</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D111" s="6">
         <v>3572569</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E111" s="6">
         <v>2850348</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F111" s="6">
         <v>959341</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G111" s="6">
         <v>1505499</v>
       </c>
-      <c r="H91" s="6">
+      <c r="H111" s="6">
         <v>290471</v>
       </c>
-      <c r="I91" s="6">
+      <c r="I111" s="6">
         <v>127799</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J111" s="1">
+        <v>245428</v>
+      </c>
+      <c r="K111" t="s">
         <v>11</v>
       </c>
     </row>

--- a/population_trend_tidy.xlsx
+++ b/population_trend_tidy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{FCE9BF43-62DD-4509-B6FF-9613F1B348D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D61F55DB-8198-46EE-B939-FE7C19B77081}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{FCE9BF43-62DD-4509-B6FF-9613F1B348D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02C8F75C-9747-478A-85DF-5B59BA37871A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5501DCC4-4A47-42B3-ABCF-C5797380A6BC}"/>
   </bookViews>
